--- a/src/excel/resultados.xlsx
+++ b/src/excel/resultados.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="483">
   <si>
     <t>Localidad</t>
   </si>
@@ -795,6 +795,33 @@
   </si>
   <si>
     <t>80254094</t>
+  </si>
+  <si>
+    <t>Vanessa gil gomez</t>
+  </si>
+  <si>
+    <t>1017142144</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liliana Sánchez Bohórquez </t>
+  </si>
+  <si>
+    <t>51988307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nelly del Rosario Espinosa Espinosa </t>
+  </si>
+  <si>
+    <t>23161656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luz Claudia cardenas rubio </t>
+  </si>
+  <si>
+    <t>65738337</t>
   </si>
   <si>
     <t>Grupo poblacional</t>
@@ -1754,7 +1781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="1"/>
@@ -4599,6 +4626,110 @@
       </c>
       <c r="H109" t="s">
         <v>221</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>43</v>
+      </c>
+      <c r="B110" t="s">
+        <v>44</v>
+      </c>
+      <c r="C110" t="s">
+        <v>10</v>
+      </c>
+      <c r="D110">
+        <v>2194</v>
+      </c>
+      <c r="E110" t="s">
+        <v>260</v>
+      </c>
+      <c r="F110" t="s">
+        <v>12</v>
+      </c>
+      <c r="G110" t="s">
+        <v>261</v>
+      </c>
+      <c r="H110" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>43</v>
+      </c>
+      <c r="B111" t="s">
+        <v>44</v>
+      </c>
+      <c r="C111" t="s">
+        <v>15</v>
+      </c>
+      <c r="D111">
+        <v>1241</v>
+      </c>
+      <c r="E111" t="s">
+        <v>263</v>
+      </c>
+      <c r="F111" t="s">
+        <v>12</v>
+      </c>
+      <c r="G111" t="s">
+        <v>264</v>
+      </c>
+      <c r="H111" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>43</v>
+      </c>
+      <c r="B112" t="s">
+        <v>44</v>
+      </c>
+      <c r="C112" t="s">
+        <v>18</v>
+      </c>
+      <c r="D112">
+        <v>599</v>
+      </c>
+      <c r="E112" t="s">
+        <v>265</v>
+      </c>
+      <c r="F112" t="s">
+        <v>12</v>
+      </c>
+      <c r="G112" t="s">
+        <v>266</v>
+      </c>
+      <c r="H112" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>43</v>
+      </c>
+      <c r="B113" t="s">
+        <v>44</v>
+      </c>
+      <c r="C113" t="s">
+        <v>21</v>
+      </c>
+      <c r="D113">
+        <v>2172</v>
+      </c>
+      <c r="E113" t="s">
+        <v>267</v>
+      </c>
+      <c r="F113" t="s">
+        <v>12</v>
+      </c>
+      <c r="G113" t="s">
+        <v>268</v>
+      </c>
+      <c r="H113" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -4623,10 +4754,10 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="B1" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -4649,10 +4780,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B2" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -4661,13 +4792,13 @@
         <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="H2" t="s">
         <v>87</v>
@@ -4675,10 +4806,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B3" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -4687,13 +4818,13 @@
         <v>1108</v>
       </c>
       <c r="E3" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="H3" t="s">
         <v>87</v>
@@ -4701,10 +4832,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B4" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -4713,13 +4844,13 @@
         <v>1283</v>
       </c>
       <c r="E4" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="H4" t="s">
         <v>87</v>
@@ -4727,10 +4858,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B5" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
@@ -4739,13 +4870,13 @@
         <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="H5" t="s">
         <v>87</v>
@@ -4753,10 +4884,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B6" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -4765,13 +4896,13 @@
         <v>1050</v>
       </c>
       <c r="E6" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="H6" t="s">
         <v>87</v>
@@ -4779,10 +4910,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B7" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -4791,13 +4922,13 @@
         <v>1941</v>
       </c>
       <c r="E7" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="H7" t="s">
         <v>87</v>
@@ -4805,10 +4936,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B8" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -4817,13 +4948,13 @@
         <v>1467</v>
       </c>
       <c r="E8" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="H8" t="s">
         <v>87</v>
@@ -4831,10 +4962,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B9" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C9" t="s">
         <v>21</v>
@@ -4843,13 +4974,13 @@
         <v>2156</v>
       </c>
       <c r="E9" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="H9" t="s">
         <v>87</v>
@@ -4857,10 +4988,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B10" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -4869,13 +5000,13 @@
         <v>1843</v>
       </c>
       <c r="E10" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="H10" t="s">
         <v>87</v>
@@ -4883,10 +5014,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B11" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C11" t="s">
         <v>15</v>
@@ -4895,13 +5026,13 @@
         <v>1006</v>
       </c>
       <c r="E11" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="H11" t="s">
         <v>87</v>
@@ -4909,10 +5040,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B12" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
@@ -4921,13 +5052,13 @@
         <v>2576</v>
       </c>
       <c r="E12" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="H12" t="s">
         <v>87</v>
@@ -4935,10 +5066,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B13" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C13" t="s">
         <v>21</v>
@@ -4947,13 +5078,13 @@
         <v>1245</v>
       </c>
       <c r="E13" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="H13" t="s">
         <v>87</v>
@@ -4961,10 +5092,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B14" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -4973,13 +5104,13 @@
         <v>383</v>
       </c>
       <c r="E14" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="H14" t="s">
         <v>87</v>
@@ -4987,10 +5118,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B15" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
@@ -4999,13 +5130,13 @@
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="H15" t="s">
         <v>87</v>
@@ -5013,10 +5144,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B16" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
@@ -5025,13 +5156,13 @@
         <v>244</v>
       </c>
       <c r="E16" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
       </c>
       <c r="G16" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="H16" t="s">
         <v>87</v>
@@ -5039,10 +5170,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B17" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C17" t="s">
         <v>21</v>
@@ -5051,13 +5182,13 @@
         <v>1656</v>
       </c>
       <c r="E17" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="H17" t="s">
         <v>87</v>
@@ -5065,10 +5196,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B18" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -5077,13 +5208,13 @@
         <v>331</v>
       </c>
       <c r="E18" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="F18" t="s">
         <v>12</v>
       </c>
       <c r="G18" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="H18" t="s">
         <v>87</v>
@@ -5091,10 +5222,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B19" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C19" t="s">
         <v>15</v>
@@ -5103,13 +5234,13 @@
         <v>97</v>
       </c>
       <c r="E19" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="H19" t="s">
         <v>87</v>
@@ -5117,10 +5248,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B20" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C20" t="s">
         <v>18</v>
@@ -5129,13 +5260,13 @@
         <v>391</v>
       </c>
       <c r="E20" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
       </c>
       <c r="G20" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="H20" t="s">
         <v>87</v>
@@ -5143,10 +5274,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B21" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C21" t="s">
         <v>21</v>
@@ -5155,13 +5286,13 @@
         <v>449</v>
       </c>
       <c r="E21" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="F21" t="s">
         <v>12</v>
       </c>
       <c r="G21" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="H21" t="s">
         <v>87</v>
@@ -5169,10 +5300,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>299</v>
+      </c>
+      <c r="B22" t="s">
         <v>290</v>
-      </c>
-      <c r="B22" t="s">
-        <v>281</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -5181,13 +5312,13 @@
         <v>2282</v>
       </c>
       <c r="E22" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="F22" t="s">
         <v>12</v>
       </c>
       <c r="G22" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="H22" t="s">
         <v>87</v>
@@ -5195,10 +5326,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>299</v>
+      </c>
+      <c r="B23" t="s">
         <v>290</v>
-      </c>
-      <c r="B23" t="s">
-        <v>281</v>
       </c>
       <c r="C23" t="s">
         <v>15</v>
@@ -5207,13 +5338,13 @@
         <v>1243</v>
       </c>
       <c r="E23" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="F23" t="s">
         <v>12</v>
       </c>
       <c r="G23" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="H23" t="s">
         <v>87</v>
@@ -5221,10 +5352,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>299</v>
+      </c>
+      <c r="B24" t="s">
         <v>290</v>
-      </c>
-      <c r="B24" t="s">
-        <v>281</v>
       </c>
       <c r="C24" t="s">
         <v>18</v>
@@ -5233,13 +5364,13 @@
         <v>1193</v>
       </c>
       <c r="E24" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="F24" t="s">
         <v>12</v>
       </c>
       <c r="G24" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="H24" t="s">
         <v>87</v>
@@ -5247,10 +5378,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>299</v>
+      </c>
+      <c r="B25" t="s">
         <v>290</v>
-      </c>
-      <c r="B25" t="s">
-        <v>281</v>
       </c>
       <c r="C25" t="s">
         <v>21</v>
@@ -5259,13 +5390,13 @@
         <v>1369</v>
       </c>
       <c r="E25" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F25" t="s">
         <v>12</v>
       </c>
       <c r="G25" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="H25" t="s">
         <v>87</v>
@@ -5273,10 +5404,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B26" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
@@ -5285,13 +5416,13 @@
         <v>415</v>
       </c>
       <c r="E26" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="F26" t="s">
         <v>12</v>
       </c>
       <c r="G26" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="H26" t="s">
         <v>87</v>
@@ -5299,10 +5430,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B27" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C27" t="s">
         <v>15</v>
@@ -5311,13 +5442,13 @@
         <v>181</v>
       </c>
       <c r="E27" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="F27" t="s">
         <v>12</v>
       </c>
       <c r="G27" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="H27" t="s">
         <v>87</v>
@@ -5325,10 +5456,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B28" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C28" t="s">
         <v>18</v>
@@ -5337,13 +5468,13 @@
         <v>1112</v>
       </c>
       <c r="E28" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F28" t="s">
         <v>12</v>
       </c>
       <c r="G28" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="H28" t="s">
         <v>87</v>
@@ -5351,10 +5482,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B29" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C29" t="s">
         <v>21</v>
@@ -5363,13 +5494,13 @@
         <v>2039</v>
       </c>
       <c r="E29" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="F29" t="s">
         <v>12</v>
       </c>
       <c r="G29" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="H29" t="s">
         <v>87</v>
@@ -5377,10 +5508,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B30" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
@@ -5389,13 +5520,13 @@
         <v>1287</v>
       </c>
       <c r="E30" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="F30" t="s">
         <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="H30" t="s">
         <v>87</v>
@@ -5403,10 +5534,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B31" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C31" t="s">
         <v>15</v>
@@ -5415,13 +5546,13 @@
         <v>1584</v>
       </c>
       <c r="E31" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="F31" t="s">
         <v>12</v>
       </c>
       <c r="G31" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="H31" t="s">
         <v>87</v>
@@ -5429,10 +5560,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -5441,13 +5572,13 @@
         <v>220</v>
       </c>
       <c r="E32" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="F32" t="s">
         <v>12</v>
       </c>
       <c r="G32" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="H32" t="s">
         <v>87</v>
@@ -5455,10 +5586,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B33" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C33" t="s">
         <v>21</v>
@@ -5467,13 +5598,13 @@
         <v>55</v>
       </c>
       <c r="E33" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="F33" t="s">
         <v>12</v>
       </c>
       <c r="G33" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="H33" t="s">
         <v>87</v>
@@ -5481,10 +5612,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B34" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
@@ -5493,13 +5624,13 @@
         <v>2458</v>
       </c>
       <c r="E34" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="F34" t="s">
         <v>12</v>
       </c>
       <c r="G34" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="H34" t="s">
         <v>87</v>
@@ -5507,10 +5638,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B35" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C35" t="s">
         <v>15</v>
@@ -5519,13 +5650,13 @@
         <v>111</v>
       </c>
       <c r="E35" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="F35" t="s">
         <v>12</v>
       </c>
       <c r="G35" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="H35" t="s">
         <v>87</v>
@@ -5533,10 +5664,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C36" t="s">
         <v>18</v>
@@ -5545,13 +5676,13 @@
         <v>908</v>
       </c>
       <c r="E36" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="F36" t="s">
         <v>12</v>
       </c>
       <c r="G36" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="H36" t="s">
         <v>87</v>
@@ -5559,10 +5690,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B37" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C37" t="s">
         <v>21</v>
@@ -5571,13 +5702,13 @@
         <v>1289</v>
       </c>
       <c r="E37" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="F37" t="s">
         <v>12</v>
       </c>
       <c r="G37" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="H37" t="s">
         <v>87</v>
@@ -5585,10 +5716,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C38" t="s">
         <v>10</v>
@@ -5597,13 +5728,13 @@
         <v>184</v>
       </c>
       <c r="E38" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="F38" t="s">
         <v>12</v>
       </c>
       <c r="G38" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="H38" t="s">
         <v>87</v>
@@ -5611,10 +5742,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C39" t="s">
         <v>15</v>
@@ -5623,13 +5754,13 @@
         <v>320</v>
       </c>
       <c r="E39" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="F39" t="s">
         <v>12</v>
       </c>
       <c r="G39" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="H39" t="s">
         <v>87</v>
@@ -5637,10 +5768,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B40" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C40" t="s">
         <v>18</v>
@@ -5649,13 +5780,13 @@
         <v>1121</v>
       </c>
       <c r="E40" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="F40" t="s">
         <v>12</v>
       </c>
       <c r="G40" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="H40" t="s">
         <v>87</v>
@@ -5663,10 +5794,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B41" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C41" t="s">
         <v>21</v>
@@ -5675,13 +5806,13 @@
         <v>396</v>
       </c>
       <c r="E41" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="F41" t="s">
         <v>12</v>
       </c>
       <c r="G41" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="H41" t="s">
         <v>87</v>
@@ -5689,10 +5820,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C42" t="s">
         <v>10</v>
@@ -5701,13 +5832,13 @@
         <v>2366</v>
       </c>
       <c r="E42" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="F42" t="s">
         <v>12</v>
       </c>
       <c r="G42" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="H42" t="s">
         <v>87</v>
@@ -5715,10 +5846,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B43" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C43" t="s">
         <v>15</v>
@@ -5727,13 +5858,13 @@
         <v>1496</v>
       </c>
       <c r="E43" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="F43" t="s">
         <v>12</v>
       </c>
       <c r="G43" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="H43" t="s">
         <v>87</v>
@@ -5741,10 +5872,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B44" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C44" t="s">
         <v>18</v>
@@ -5753,13 +5884,13 @@
         <v>77</v>
       </c>
       <c r="E44" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="F44" t="s">
         <v>12</v>
       </c>
       <c r="G44" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="H44" t="s">
         <v>87</v>
@@ -5767,10 +5898,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B45" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C45" t="s">
         <v>21</v>
@@ -5779,13 +5910,13 @@
         <v>1918</v>
       </c>
       <c r="E45" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="F45" t="s">
         <v>12</v>
       </c>
       <c r="G45" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H45" t="s">
         <v>87</v>
@@ -5793,10 +5924,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B46" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C46" t="s">
         <v>10</v>
@@ -5805,13 +5936,13 @@
         <v>2651</v>
       </c>
       <c r="E46" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="F46" t="s">
         <v>12</v>
       </c>
       <c r="G46" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="H46" t="s">
         <v>87</v>
@@ -5819,10 +5950,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B47" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C47" t="s">
         <v>15</v>
@@ -5831,13 +5962,13 @@
         <v>508</v>
       </c>
       <c r="E47" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="F47" t="s">
         <v>12</v>
       </c>
       <c r="G47" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="H47" t="s">
         <v>87</v>
@@ -5845,10 +5976,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B48" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C48" t="s">
         <v>18</v>
@@ -5857,13 +5988,13 @@
         <v>2003</v>
       </c>
       <c r="E48" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="F48" t="s">
         <v>12</v>
       </c>
       <c r="G48" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="H48" t="s">
         <v>87</v>
@@ -5871,10 +6002,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B49" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C49" t="s">
         <v>21</v>
@@ -5883,13 +6014,13 @@
         <v>1019</v>
       </c>
       <c r="E49" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="F49" t="s">
         <v>12</v>
       </c>
       <c r="G49" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="H49" t="s">
         <v>87</v>
@@ -5897,10 +6028,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B50" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C50" t="s">
         <v>10</v>
@@ -5909,13 +6040,13 @@
         <v>1930</v>
       </c>
       <c r="E50" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="F50" t="s">
         <v>12</v>
       </c>
       <c r="G50" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="H50" t="s">
         <v>87</v>
@@ -5923,10 +6054,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B51" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C51" t="s">
         <v>15</v>
@@ -5935,13 +6066,13 @@
         <v>330</v>
       </c>
       <c r="E51" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="F51" t="s">
         <v>12</v>
       </c>
       <c r="G51" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="H51" t="s">
         <v>87</v>
@@ -5949,10 +6080,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B52" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C52" t="s">
         <v>18</v>
@@ -5961,13 +6092,13 @@
         <v>589</v>
       </c>
       <c r="E52" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="F52" t="s">
         <v>12</v>
       </c>
       <c r="G52" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="H52" t="s">
         <v>87</v>
@@ -5975,10 +6106,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B53" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C53" t="s">
         <v>21</v>
@@ -5987,13 +6118,13 @@
         <v>1728</v>
       </c>
       <c r="E53" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
       </c>
       <c r="G53" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="H53" t="s">
         <v>87</v>
@@ -6001,10 +6132,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B54" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C54" t="s">
         <v>10</v>
@@ -6013,13 +6144,13 @@
         <v>1446</v>
       </c>
       <c r="E54" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="F54" t="s">
         <v>12</v>
       </c>
       <c r="G54" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="H54" t="s">
         <v>87</v>
@@ -6027,10 +6158,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B55" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C55" t="s">
         <v>15</v>
@@ -6039,13 +6170,13 @@
         <v>2072</v>
       </c>
       <c r="E55" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="F55" t="s">
         <v>12</v>
       </c>
       <c r="G55" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="H55" t="s">
         <v>87</v>
@@ -6053,10 +6184,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B56" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C56" t="s">
         <v>18</v>
@@ -6065,13 +6196,13 @@
         <v>183</v>
       </c>
       <c r="E56" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="F56" t="s">
         <v>12</v>
       </c>
       <c r="G56" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="H56" t="s">
         <v>87</v>
@@ -6079,10 +6210,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B57" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C57" t="s">
         <v>21</v>
@@ -6091,13 +6222,13 @@
         <v>2310</v>
       </c>
       <c r="E57" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="F57" t="s">
         <v>12</v>
       </c>
       <c r="G57" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="H57" t="s">
         <v>87</v>
@@ -6105,10 +6236,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B58" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C58" t="s">
         <v>10</v>
@@ -6117,13 +6248,13 @@
         <v>2328</v>
       </c>
       <c r="E58" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="F58" t="s">
         <v>12</v>
       </c>
       <c r="G58" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="H58" t="s">
         <v>87</v>
@@ -6131,10 +6262,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B59" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C59" t="s">
         <v>15</v>
@@ -6143,13 +6274,13 @@
         <v>1472</v>
       </c>
       <c r="E59" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F59" t="s">
         <v>12</v>
       </c>
       <c r="G59" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="H59" t="s">
         <v>87</v>
@@ -6157,10 +6288,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B60" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C60" t="s">
         <v>18</v>
@@ -6169,13 +6300,13 @@
         <v>2370</v>
       </c>
       <c r="E60" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="F60" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="G60" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="H60" t="s">
         <v>87</v>
@@ -6183,10 +6314,10 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C61" t="s">
         <v>21</v>
@@ -6195,13 +6326,13 @@
         <v>1145</v>
       </c>
       <c r="E61" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="F61" t="s">
         <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="H61" t="s">
         <v>87</v>
@@ -6209,10 +6340,10 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B62" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C62" t="s">
         <v>10</v>
@@ -6221,13 +6352,13 @@
         <v>1408</v>
       </c>
       <c r="E62" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F62" t="s">
         <v>35</v>
       </c>
       <c r="G62" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="H62" t="s">
         <v>87</v>
@@ -6235,10 +6366,10 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B63" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C63" t="s">
         <v>15</v>
@@ -6247,13 +6378,13 @@
         <v>20</v>
       </c>
       <c r="E63" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="F63" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="G63" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="H63" t="s">
         <v>87</v>
@@ -6261,10 +6392,10 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B64" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C64" t="s">
         <v>18</v>
@@ -6273,13 +6404,13 @@
         <v>32</v>
       </c>
       <c r="E64" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="F64" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="G64" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="H64" t="s">
         <v>87</v>
@@ -6287,10 +6418,10 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B65" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C65" t="s">
         <v>21</v>
@@ -6299,13 +6430,13 @@
         <v>1344</v>
       </c>
       <c r="E65" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="F65" t="s">
         <v>12</v>
       </c>
       <c r="G65" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="H65" t="s">
         <v>87</v>
@@ -6313,10 +6444,10 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B66" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C66" t="s">
         <v>10</v>
@@ -6325,13 +6456,13 @@
         <v>2227</v>
       </c>
       <c r="E66" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="F66" t="s">
         <v>35</v>
       </c>
       <c r="G66" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="H66" t="s">
         <v>87</v>
@@ -6339,10 +6470,10 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B67" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C67" t="s">
         <v>15</v>
@@ -6351,13 +6482,13 @@
         <v>169</v>
       </c>
       <c r="E67" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="F67" t="s">
         <v>35</v>
       </c>
       <c r="G67" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="H67" t="s">
         <v>87</v>
@@ -6365,10 +6496,10 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B68" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C68" t="s">
         <v>18</v>
@@ -6377,13 +6508,13 @@
         <v>87</v>
       </c>
       <c r="E68" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="F68" t="s">
         <v>12</v>
       </c>
       <c r="G68" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="H68" t="s">
         <v>87</v>
@@ -6391,10 +6522,10 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B69" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C69" t="s">
         <v>21</v>
@@ -6403,13 +6534,13 @@
         <v>740</v>
       </c>
       <c r="E69" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="F69" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="G69" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="H69" t="s">
         <v>87</v>
@@ -6417,10 +6548,10 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B70" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C70" t="s">
         <v>10</v>
@@ -6429,13 +6560,13 @@
         <v>1110</v>
       </c>
       <c r="E70" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="F70" t="s">
         <v>12</v>
       </c>
       <c r="G70" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="H70" t="s">
         <v>87</v>
@@ -6443,10 +6574,10 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B71" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C71" t="s">
         <v>15</v>
@@ -6455,13 +6586,13 @@
         <v>950</v>
       </c>
       <c r="E71" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="F71" t="s">
         <v>12</v>
       </c>
       <c r="G71" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="H71" t="s">
         <v>87</v>
@@ -6469,10 +6600,10 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B72" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C72" t="s">
         <v>18</v>
@@ -6481,13 +6612,13 @@
         <v>1164</v>
       </c>
       <c r="E72" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="F72" t="s">
         <v>12</v>
       </c>
       <c r="G72" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="H72" t="s">
         <v>87</v>
@@ -6495,10 +6626,10 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B73" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C73" t="s">
         <v>21</v>
@@ -6507,13 +6638,13 @@
         <v>84</v>
       </c>
       <c r="E73" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="F73" t="s">
         <v>12</v>
       </c>
       <c r="G73" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="H73" t="s">
         <v>87</v>
@@ -6521,10 +6652,10 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B74" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C74" t="s">
         <v>10</v>
@@ -6533,13 +6664,13 @@
         <v>1319</v>
       </c>
       <c r="E74" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="F74" t="s">
         <v>12</v>
       </c>
       <c r="G74" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="H74" t="s">
         <v>87</v>
@@ -6547,10 +6678,10 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B75" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C75" t="s">
         <v>15</v>
@@ -6559,13 +6690,13 @@
         <v>1248</v>
       </c>
       <c r="E75" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="F75" t="s">
         <v>12</v>
       </c>
       <c r="G75" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="H75" t="s">
         <v>87</v>
@@ -6573,10 +6704,10 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B76" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C76" t="s">
         <v>18</v>
@@ -6585,13 +6716,13 @@
         <v>2010</v>
       </c>
       <c r="E76" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="F76" t="s">
         <v>12</v>
       </c>
       <c r="G76" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="H76" t="s">
         <v>87</v>
@@ -6599,10 +6730,10 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B77" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C77" t="s">
         <v>21</v>
@@ -6611,13 +6742,13 @@
         <v>139</v>
       </c>
       <c r="E77" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F77" t="s">
         <v>12</v>
       </c>
       <c r="G77" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="H77" t="s">
         <v>87</v>
@@ -6625,10 +6756,10 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="B78" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C78" t="s">
         <v>10</v>
@@ -6637,13 +6768,13 @@
         <v>2769</v>
       </c>
       <c r="E78" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F78" t="s">
         <v>12</v>
       </c>
       <c r="G78" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="H78" t="s">
         <v>87</v>
@@ -6651,10 +6782,10 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="B79" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C79" t="s">
         <v>15</v>
@@ -6663,13 +6794,13 @@
         <v>2772</v>
       </c>
       <c r="E79" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="F79" t="s">
         <v>12</v>
       </c>
       <c r="G79" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="H79" t="s">
         <v>87</v>
@@ -6677,10 +6808,10 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="B80" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C80" t="s">
         <v>18</v>
@@ -6689,13 +6820,13 @@
         <v>2771</v>
       </c>
       <c r="E80" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="F80" t="s">
         <v>12</v>
       </c>
       <c r="G80" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="H80" t="s">
         <v>87</v>
@@ -6703,10 +6834,10 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="B81" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C81" t="s">
         <v>21</v>
@@ -6715,13 +6846,13 @@
         <v>2770</v>
       </c>
       <c r="E81" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="F81" t="s">
         <v>12</v>
       </c>
       <c r="G81" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="H81" t="s">
         <v>87</v>
@@ -6729,10 +6860,10 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B82" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C82" t="s">
         <v>10</v>
@@ -6741,13 +6872,13 @@
         <v>15</v>
       </c>
       <c r="E82" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F82" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G82" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="H82" t="s">
         <v>87</v>
@@ -6755,10 +6886,10 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B83" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C83" t="s">
         <v>15</v>
@@ -6767,13 +6898,13 @@
         <v>33</v>
       </c>
       <c r="E83" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F83" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G83" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="H83" t="s">
         <v>87</v>
@@ -6781,10 +6912,10 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B84" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C84" t="s">
         <v>18</v>
@@ -6793,13 +6924,13 @@
         <v>27</v>
       </c>
       <c r="E84" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F84" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G84" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="H84" t="s">
         <v>87</v>
@@ -6807,10 +6938,10 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B85" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C85" t="s">
         <v>21</v>
@@ -6819,13 +6950,13 @@
         <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F85" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G85" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="H85" t="s">
         <v>87</v>
@@ -6833,10 +6964,10 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B86" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C86" t="s">
         <v>10</v>
@@ -6845,13 +6976,13 @@
         <v>28</v>
       </c>
       <c r="E86" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F86" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G86" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="H86" t="s">
         <v>87</v>
@@ -6859,10 +6990,10 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B87" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C87" t="s">
         <v>15</v>
@@ -6871,13 +7002,13 @@
         <v>19</v>
       </c>
       <c r="E87" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F87" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G87" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="H87" t="s">
         <v>87</v>
@@ -6885,10 +7016,10 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B88" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C88" t="s">
         <v>18</v>
@@ -6897,13 +7028,13 @@
         <v>9</v>
       </c>
       <c r="E88" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F88" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G88" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="H88" t="s">
         <v>87</v>
@@ -6911,10 +7042,10 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B89" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C89" t="s">
         <v>21</v>
@@ -6923,13 +7054,13 @@
         <v>5</v>
       </c>
       <c r="E89" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F89" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G89" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="H89" t="s">
         <v>87</v>
@@ -6937,10 +7068,10 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B90" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C90" t="s">
         <v>10</v>
@@ -6949,13 +7080,13 @@
         <v>2</v>
       </c>
       <c r="E90" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F90" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G90" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="H90" t="s">
         <v>87</v>
@@ -6963,10 +7094,10 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B91" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C91" t="s">
         <v>15</v>
@@ -6975,13 +7106,13 @@
         <v>26</v>
       </c>
       <c r="E91" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F91" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G91" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="H91" t="s">
         <v>87</v>
@@ -6989,10 +7120,10 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B92" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C92" t="s">
         <v>18</v>
@@ -7001,13 +7132,13 @@
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F92" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G92" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="H92" t="s">
         <v>87</v>
@@ -7015,10 +7146,10 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B93" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C93" t="s">
         <v>21</v>
@@ -7027,13 +7158,13 @@
         <v>35</v>
       </c>
       <c r="E93" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F93" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G93" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="H93" t="s">
         <v>87</v>
@@ -7041,10 +7172,10 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B94" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="C94" t="s">
         <v>10</v>
@@ -7053,13 +7184,13 @@
         <v>10</v>
       </c>
       <c r="E94" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F94" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G94" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="H94" t="s">
         <v>87</v>
@@ -7067,10 +7198,10 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B95" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="C95" t="s">
         <v>15</v>
@@ -7079,13 +7210,13 @@
         <v>20</v>
       </c>
       <c r="E95" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F95" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G95" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="H95" t="s">
         <v>87</v>
@@ -7093,10 +7224,10 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B96" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="C96" t="s">
         <v>18</v>
@@ -7105,13 +7236,13 @@
         <v>23</v>
       </c>
       <c r="E96" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F96" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G96" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="H96" t="s">
         <v>87</v>
@@ -7119,10 +7250,10 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B97" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="C97" t="s">
         <v>21</v>
@@ -7131,13 +7262,13 @@
         <v>44</v>
       </c>
       <c r="E97" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F97" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G97" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="H97" t="s">
         <v>87</v>
@@ -7145,10 +7276,10 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B98" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C98" t="s">
         <v>10</v>
@@ -7157,13 +7288,13 @@
         <v>462</v>
       </c>
       <c r="E98" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="F98" t="s">
         <v>12</v>
       </c>
       <c r="G98" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="H98" t="s">
         <v>221</v>
@@ -7171,10 +7302,10 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B99" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C99" t="s">
         <v>15</v>
@@ -7183,13 +7314,13 @@
         <v>1099</v>
       </c>
       <c r="E99" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="F99" t="s">
         <v>12</v>
       </c>
       <c r="G99" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="H99" t="s">
         <v>221</v>
@@ -7197,10 +7328,10 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B100" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C100" t="s">
         <v>18</v>
@@ -7209,13 +7340,13 @@
         <v>1790</v>
       </c>
       <c r="E100" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="F100" t="s">
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="H100" t="s">
         <v>221</v>
@@ -7223,10 +7354,10 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B101" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C101" t="s">
         <v>21</v>
@@ -7235,13 +7366,13 @@
         <v>2284</v>
       </c>
       <c r="E101" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="F101" t="s">
         <v>12</v>
       </c>
       <c r="G101" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="H101" t="s">
         <v>221</v>
@@ -7249,10 +7380,10 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B102" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C102" t="s">
         <v>10</v>
@@ -7261,13 +7392,13 @@
         <v>2662</v>
       </c>
       <c r="E102" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="F102" t="s">
         <v>12</v>
       </c>
       <c r="G102" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="H102" t="s">
         <v>221</v>
@@ -7275,10 +7406,10 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B103" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C103" t="s">
         <v>15</v>
@@ -7287,13 +7418,13 @@
         <v>43</v>
       </c>
       <c r="E103" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="F103" t="s">
         <v>12</v>
       </c>
       <c r="G103" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="H103" t="s">
         <v>221</v>
@@ -7301,10 +7432,10 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B104" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C104" t="s">
         <v>18</v>
@@ -7313,13 +7444,13 @@
         <v>1432</v>
       </c>
       <c r="E104" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="F104" t="s">
         <v>12</v>
       </c>
       <c r="G104" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="H104" t="s">
         <v>221</v>
@@ -7327,10 +7458,10 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B105" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C105" t="s">
         <v>21</v>
@@ -7339,13 +7470,13 @@
         <v>566</v>
       </c>
       <c r="E105" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="F105" t="s">
         <v>12</v>
       </c>
       <c r="G105" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="H105" t="s">
         <v>221</v>
@@ -7353,10 +7484,10 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B106" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C106" t="s">
         <v>10</v>
@@ -7365,13 +7496,13 @@
         <v>278</v>
       </c>
       <c r="E106" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="F106" t="s">
         <v>12</v>
       </c>
       <c r="G106" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="H106" t="s">
         <v>221</v>
@@ -7379,10 +7510,10 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B107" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C107" t="s">
         <v>15</v>
@@ -7391,13 +7522,13 @@
         <v>428</v>
       </c>
       <c r="E107" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="F107" t="s">
         <v>12</v>
       </c>
       <c r="G107" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="H107" t="s">
         <v>221</v>
@@ -7405,10 +7536,10 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B108" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C108" t="s">
         <v>18</v>
@@ -7417,13 +7548,13 @@
         <v>2745</v>
       </c>
       <c r="E108" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="F108" t="s">
         <v>12</v>
       </c>
       <c r="G108" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="H108" t="s">
         <v>221</v>
@@ -7431,10 +7562,10 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B109" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C109" t="s">
         <v>21</v>
@@ -7443,13 +7574,13 @@
         <v>1050</v>
       </c>
       <c r="E109" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="F109" t="s">
         <v>12</v>
       </c>
       <c r="G109" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="H109" t="s">
         <v>221</v>

--- a/src/excel/resultados.xlsx
+++ b/src/excel/resultados.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="520">
   <si>
     <t>Localidad</t>
   </si>
@@ -824,6 +824,96 @@
     <t>65738337</t>
   </si>
   <si>
+    <t>Alejandra Martinez</t>
+  </si>
+  <si>
+    <t>1233490850</t>
+  </si>
+  <si>
+    <t>Valentina Perafán Javela</t>
+  </si>
+  <si>
+    <t>1030690304</t>
+  </si>
+  <si>
+    <t>Semana Espinosa Sanchez</t>
+  </si>
+  <si>
+    <t>1025536539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loren Viviana Peñaloza Estupiñan </t>
+  </si>
+  <si>
+    <t>1019992598</t>
+  </si>
+  <si>
+    <t>JUAN ESTEBAN RODRIGUEZ MATEUS</t>
+  </si>
+  <si>
+    <t>1013102340</t>
+  </si>
+  <si>
+    <t>Henry David Cardozo Vesga</t>
+  </si>
+  <si>
+    <t>1030698984</t>
+  </si>
+  <si>
+    <t>Julián Mier Gama</t>
+  </si>
+  <si>
+    <t>1030694294</t>
+  </si>
+  <si>
+    <t>Andres Castellanos</t>
+  </si>
+  <si>
+    <t>1010003244</t>
+  </si>
+  <si>
+    <t>Olga Patricia Torres</t>
+  </si>
+  <si>
+    <t>52060237</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Velazquez Buritrago</t>
+  </si>
+  <si>
+    <t>1018459631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diana Maritza Mondragon </t>
+  </si>
+  <si>
+    <t>52897782</t>
+  </si>
+  <si>
+    <t>Rosario Soto</t>
+  </si>
+  <si>
+    <t>39651997</t>
+  </si>
+  <si>
+    <t>Merlín Soto</t>
+  </si>
+  <si>
+    <t>16609550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alirio Alfonso Peña Sánchez  </t>
+  </si>
+  <si>
+    <t>3032507</t>
+  </si>
+  <si>
+    <t>FERNANDO MONTENEGRO BELTRAN</t>
+  </si>
+  <si>
+    <t>79043763</t>
+  </si>
+  <si>
     <t>Grupo poblacional</t>
   </si>
   <si>
@@ -1464,6 +1554,27 @@
   </si>
   <si>
     <t>1032479038</t>
+  </si>
+  <si>
+    <t>1013131942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1033732456 </t>
+  </si>
+  <si>
+    <t>1013127382</t>
+  </si>
+  <si>
+    <t>1028700540</t>
+  </si>
+  <si>
+    <t>1145226108</t>
+  </si>
+  <si>
+    <t>1028491061</t>
+  </si>
+  <si>
+    <t>1019904632</t>
   </si>
 </sst>
 </file>
@@ -1781,7 +1892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="1"/>
@@ -4732,6 +4843,422 @@
         <v>262</v>
       </c>
     </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>130</v>
+      </c>
+      <c r="B114" t="s">
+        <v>65</v>
+      </c>
+      <c r="C114" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114">
+        <v>1743</v>
+      </c>
+      <c r="E114" t="s">
+        <v>269</v>
+      </c>
+      <c r="F114" t="s">
+        <v>12</v>
+      </c>
+      <c r="G114" t="s">
+        <v>270</v>
+      </c>
+      <c r="H114" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>130</v>
+      </c>
+      <c r="B115" t="s">
+        <v>65</v>
+      </c>
+      <c r="C115" t="s">
+        <v>15</v>
+      </c>
+      <c r="D115">
+        <v>1489</v>
+      </c>
+      <c r="E115" t="s">
+        <v>271</v>
+      </c>
+      <c r="F115" t="s">
+        <v>12</v>
+      </c>
+      <c r="G115" t="s">
+        <v>272</v>
+      </c>
+      <c r="H115" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>130</v>
+      </c>
+      <c r="B116" t="s">
+        <v>65</v>
+      </c>
+      <c r="C116" t="s">
+        <v>18</v>
+      </c>
+      <c r="D116">
+        <v>680</v>
+      </c>
+      <c r="E116" t="s">
+        <v>273</v>
+      </c>
+      <c r="F116" t="s">
+        <v>12</v>
+      </c>
+      <c r="G116" t="s">
+        <v>274</v>
+      </c>
+      <c r="H116" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>130</v>
+      </c>
+      <c r="B117" t="s">
+        <v>65</v>
+      </c>
+      <c r="C117" t="s">
+        <v>21</v>
+      </c>
+      <c r="D117">
+        <v>661</v>
+      </c>
+      <c r="E117" t="s">
+        <v>275</v>
+      </c>
+      <c r="F117" t="s">
+        <v>12</v>
+      </c>
+      <c r="G117" t="s">
+        <v>276</v>
+      </c>
+      <c r="H117" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>130</v>
+      </c>
+      <c r="B118" t="s">
+        <v>139</v>
+      </c>
+      <c r="C118" t="s">
+        <v>10</v>
+      </c>
+      <c r="D118">
+        <v>1929</v>
+      </c>
+      <c r="E118" t="s">
+        <v>277</v>
+      </c>
+      <c r="F118" t="s">
+        <v>12</v>
+      </c>
+      <c r="G118" t="s">
+        <v>278</v>
+      </c>
+      <c r="H118" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>130</v>
+      </c>
+      <c r="B119" t="s">
+        <v>139</v>
+      </c>
+      <c r="C119" t="s">
+        <v>15</v>
+      </c>
+      <c r="D119">
+        <v>272</v>
+      </c>
+      <c r="E119" t="s">
+        <v>279</v>
+      </c>
+      <c r="F119" t="s">
+        <v>12</v>
+      </c>
+      <c r="G119" t="s">
+        <v>280</v>
+      </c>
+      <c r="H119" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>130</v>
+      </c>
+      <c r="B120" t="s">
+        <v>139</v>
+      </c>
+      <c r="C120" t="s">
+        <v>18</v>
+      </c>
+      <c r="D120">
+        <v>270</v>
+      </c>
+      <c r="E120" t="s">
+        <v>281</v>
+      </c>
+      <c r="F120" t="s">
+        <v>12</v>
+      </c>
+      <c r="G120" t="s">
+        <v>282</v>
+      </c>
+      <c r="H120" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>130</v>
+      </c>
+      <c r="B121" t="s">
+        <v>139</v>
+      </c>
+      <c r="C121" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121">
+        <v>2277</v>
+      </c>
+      <c r="E121" t="s">
+        <v>283</v>
+      </c>
+      <c r="F121" t="s">
+        <v>12</v>
+      </c>
+      <c r="G121" t="s">
+        <v>284</v>
+      </c>
+      <c r="H121" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>130</v>
+      </c>
+      <c r="B122" t="s">
+        <v>55</v>
+      </c>
+      <c r="C122" t="s">
+        <v>10</v>
+      </c>
+      <c r="D122">
+        <v>1325</v>
+      </c>
+      <c r="E122" t="s">
+        <v>285</v>
+      </c>
+      <c r="F122" t="s">
+        <v>12</v>
+      </c>
+      <c r="G122" t="s">
+        <v>286</v>
+      </c>
+      <c r="H122" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>130</v>
+      </c>
+      <c r="B123" t="s">
+        <v>55</v>
+      </c>
+      <c r="C123" t="s">
+        <v>15</v>
+      </c>
+      <c r="D123">
+        <v>370</v>
+      </c>
+      <c r="E123" t="s">
+        <v>287</v>
+      </c>
+      <c r="F123" t="s">
+        <v>12</v>
+      </c>
+      <c r="G123" t="s">
+        <v>288</v>
+      </c>
+      <c r="H123" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>130</v>
+      </c>
+      <c r="B124" t="s">
+        <v>55</v>
+      </c>
+      <c r="C124" t="s">
+        <v>18</v>
+      </c>
+      <c r="D124">
+        <v>318</v>
+      </c>
+      <c r="E124" t="s">
+        <v>289</v>
+      </c>
+      <c r="F124" t="s">
+        <v>12</v>
+      </c>
+      <c r="G124" t="s">
+        <v>290</v>
+      </c>
+      <c r="H124" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>130</v>
+      </c>
+      <c r="B125" t="s">
+        <v>55</v>
+      </c>
+      <c r="C125" t="s">
+        <v>21</v>
+      </c>
+      <c r="D125">
+        <v>315</v>
+      </c>
+      <c r="E125" t="s">
+        <v>291</v>
+      </c>
+      <c r="F125" t="s">
+        <v>12</v>
+      </c>
+      <c r="G125" t="s">
+        <v>292</v>
+      </c>
+      <c r="H125" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>130</v>
+      </c>
+      <c r="B126" t="s">
+        <v>156</v>
+      </c>
+      <c r="C126" t="s">
+        <v>10</v>
+      </c>
+      <c r="D126">
+        <v>135</v>
+      </c>
+      <c r="E126" t="s">
+        <v>293</v>
+      </c>
+      <c r="F126" t="s">
+        <v>12</v>
+      </c>
+      <c r="G126" t="s">
+        <v>294</v>
+      </c>
+      <c r="H126" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>130</v>
+      </c>
+      <c r="B127" t="s">
+        <v>156</v>
+      </c>
+      <c r="C127" t="s">
+        <v>15</v>
+      </c>
+      <c r="D127">
+        <v>1121</v>
+      </c>
+      <c r="E127" t="s">
+        <v>295</v>
+      </c>
+      <c r="F127" t="s">
+        <v>12</v>
+      </c>
+      <c r="G127" t="s">
+        <v>296</v>
+      </c>
+      <c r="H127" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>130</v>
+      </c>
+      <c r="B128" t="s">
+        <v>156</v>
+      </c>
+      <c r="C128" t="s">
+        <v>18</v>
+      </c>
+      <c r="D128">
+        <v>603</v>
+      </c>
+      <c r="E128" t="s">
+        <v>157</v>
+      </c>
+      <c r="F128" t="s">
+        <v>12</v>
+      </c>
+      <c r="G128" t="s">
+        <v>158</v>
+      </c>
+      <c r="H128" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>130</v>
+      </c>
+      <c r="B129" t="s">
+        <v>156</v>
+      </c>
+      <c r="C129" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129">
+        <v>1297</v>
+      </c>
+      <c r="E129" t="s">
+        <v>297</v>
+      </c>
+      <c r="F129" t="s">
+        <v>12</v>
+      </c>
+      <c r="G129" t="s">
+        <v>298</v>
+      </c>
+      <c r="H129" t="s">
+        <v>262</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -4740,7 +5267,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
     <col min="1" max="1" width="24.140625" customWidth="1"/>
@@ -4754,10 +5281,10 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="B1" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -4780,10 +5307,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B2" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -4792,13 +5319,13 @@
         <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="H2" t="s">
         <v>87</v>
@@ -4806,10 +5333,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B3" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -4818,13 +5345,13 @@
         <v>1108</v>
       </c>
       <c r="E3" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="H3" t="s">
         <v>87</v>
@@ -4832,10 +5359,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -4844,13 +5371,13 @@
         <v>1283</v>
       </c>
       <c r="E4" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="H4" t="s">
         <v>87</v>
@@ -4858,10 +5385,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B5" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
@@ -4870,13 +5397,13 @@
         <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="H5" t="s">
         <v>87</v>
@@ -4884,10 +5411,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B6" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -4896,13 +5423,13 @@
         <v>1050</v>
       </c>
       <c r="E6" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="H6" t="s">
         <v>87</v>
@@ -4910,10 +5437,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B7" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -4922,13 +5449,13 @@
         <v>1941</v>
       </c>
       <c r="E7" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="H7" t="s">
         <v>87</v>
@@ -4936,10 +5463,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B8" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -4948,13 +5475,13 @@
         <v>1467</v>
       </c>
       <c r="E8" t="s">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="H8" t="s">
         <v>87</v>
@@ -4962,10 +5489,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B9" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C9" t="s">
         <v>21</v>
@@ -4974,13 +5501,13 @@
         <v>2156</v>
       </c>
       <c r="E9" t="s">
-        <v>288</v>
+        <v>318</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="H9" t="s">
         <v>87</v>
@@ -4988,10 +5515,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B10" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -5000,13 +5527,13 @@
         <v>1843</v>
       </c>
       <c r="E10" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="H10" t="s">
         <v>87</v>
@@ -5014,10 +5541,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B11" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C11" t="s">
         <v>15</v>
@@ -5026,13 +5553,13 @@
         <v>1006</v>
       </c>
       <c r="E11" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="H11" t="s">
         <v>87</v>
@@ -5040,10 +5567,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B12" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
@@ -5052,13 +5579,13 @@
         <v>2576</v>
       </c>
       <c r="E12" t="s">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="H12" t="s">
         <v>87</v>
@@ -5066,10 +5593,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B13" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C13" t="s">
         <v>21</v>
@@ -5078,13 +5605,13 @@
         <v>1245</v>
       </c>
       <c r="E13" t="s">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="H13" t="s">
         <v>87</v>
@@ -5092,10 +5619,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="B14" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -5104,13 +5631,13 @@
         <v>383</v>
       </c>
       <c r="E14" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="H14" t="s">
         <v>87</v>
@@ -5118,10 +5645,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="B15" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
@@ -5130,13 +5657,13 @@
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>302</v>
+        <v>332</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="H15" t="s">
         <v>87</v>
@@ -5144,10 +5671,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="B16" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
@@ -5156,13 +5683,13 @@
         <v>244</v>
       </c>
       <c r="E16" t="s">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
       </c>
       <c r="G16" t="s">
-        <v>305</v>
+        <v>335</v>
       </c>
       <c r="H16" t="s">
         <v>87</v>
@@ -5170,10 +5697,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="B17" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C17" t="s">
         <v>21</v>
@@ -5182,13 +5709,13 @@
         <v>1656</v>
       </c>
       <c r="E17" t="s">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>307</v>
+        <v>337</v>
       </c>
       <c r="H17" t="s">
         <v>87</v>
@@ -5196,10 +5723,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="B18" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -5208,13 +5735,13 @@
         <v>331</v>
       </c>
       <c r="E18" t="s">
-        <v>308</v>
+        <v>338</v>
       </c>
       <c r="F18" t="s">
         <v>12</v>
       </c>
       <c r="G18" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="H18" t="s">
         <v>87</v>
@@ -5222,10 +5749,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="B19" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C19" t="s">
         <v>15</v>
@@ -5234,13 +5761,13 @@
         <v>97</v>
       </c>
       <c r="E19" t="s">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="H19" t="s">
         <v>87</v>
@@ -5248,10 +5775,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="B20" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C20" t="s">
         <v>18</v>
@@ -5260,13 +5787,13 @@
         <v>391</v>
       </c>
       <c r="E20" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
       </c>
       <c r="G20" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="H20" t="s">
         <v>87</v>
@@ -5274,10 +5801,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="B21" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C21" t="s">
         <v>21</v>
@@ -5286,13 +5813,13 @@
         <v>449</v>
       </c>
       <c r="E21" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="F21" t="s">
         <v>12</v>
       </c>
       <c r="G21" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="H21" t="s">
         <v>87</v>
@@ -5300,10 +5827,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="B22" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -5312,13 +5839,13 @@
         <v>2282</v>
       </c>
       <c r="E22" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="F22" t="s">
         <v>12</v>
       </c>
       <c r="G22" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="H22" t="s">
         <v>87</v>
@@ -5326,10 +5853,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="B23" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C23" t="s">
         <v>15</v>
@@ -5338,13 +5865,13 @@
         <v>1243</v>
       </c>
       <c r="E23" t="s">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="F23" t="s">
         <v>12</v>
       </c>
       <c r="G23" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="H23" t="s">
         <v>87</v>
@@ -5352,10 +5879,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="B24" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C24" t="s">
         <v>18</v>
@@ -5364,13 +5891,13 @@
         <v>1193</v>
       </c>
       <c r="E24" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="F24" t="s">
         <v>12</v>
       </c>
       <c r="G24" t="s">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="H24" t="s">
         <v>87</v>
@@ -5378,10 +5905,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="B25" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C25" t="s">
         <v>21</v>
@@ -5390,13 +5917,13 @@
         <v>1369</v>
       </c>
       <c r="E25" t="s">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="F25" t="s">
         <v>12</v>
       </c>
       <c r="G25" t="s">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="H25" t="s">
         <v>87</v>
@@ -5404,10 +5931,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="B26" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
@@ -5416,13 +5943,13 @@
         <v>415</v>
       </c>
       <c r="E26" t="s">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="F26" t="s">
         <v>12</v>
       </c>
       <c r="G26" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="H26" t="s">
         <v>87</v>
@@ -5430,10 +5957,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="B27" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C27" t="s">
         <v>15</v>
@@ -5442,13 +5969,13 @@
         <v>181</v>
       </c>
       <c r="E27" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="F27" t="s">
         <v>12</v>
       </c>
       <c r="G27" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="H27" t="s">
         <v>87</v>
@@ -5456,10 +5983,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="B28" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C28" t="s">
         <v>18</v>
@@ -5468,13 +5995,13 @@
         <v>1112</v>
       </c>
       <c r="E28" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="F28" t="s">
         <v>12</v>
       </c>
       <c r="G28" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="H28" t="s">
         <v>87</v>
@@ -5482,10 +6009,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="B29" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C29" t="s">
         <v>21</v>
@@ -5494,13 +6021,13 @@
         <v>2039</v>
       </c>
       <c r="E29" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="F29" t="s">
         <v>12</v>
       </c>
       <c r="G29" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="H29" t="s">
         <v>87</v>
@@ -5508,10 +6035,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="B30" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
@@ -5520,13 +6047,13 @@
         <v>1287</v>
       </c>
       <c r="E30" t="s">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="F30" t="s">
         <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
       <c r="H30" t="s">
         <v>87</v>
@@ -5534,10 +6061,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="B31" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C31" t="s">
         <v>15</v>
@@ -5546,13 +6073,13 @@
         <v>1584</v>
       </c>
       <c r="E31" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="F31" t="s">
         <v>12</v>
       </c>
       <c r="G31" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="H31" t="s">
         <v>87</v>
@@ -5560,10 +6087,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="B32" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -5572,13 +6099,13 @@
         <v>220</v>
       </c>
       <c r="E32" t="s">
-        <v>337</v>
+        <v>367</v>
       </c>
       <c r="F32" t="s">
         <v>12</v>
       </c>
       <c r="G32" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="H32" t="s">
         <v>87</v>
@@ -5586,10 +6113,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="B33" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C33" t="s">
         <v>21</v>
@@ -5598,13 +6125,13 @@
         <v>55</v>
       </c>
       <c r="E33" t="s">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="F33" t="s">
         <v>12</v>
       </c>
       <c r="G33" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="H33" t="s">
         <v>87</v>
@@ -5612,10 +6139,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="B34" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
@@ -5624,13 +6151,13 @@
         <v>2458</v>
       </c>
       <c r="E34" t="s">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="F34" t="s">
         <v>12</v>
       </c>
       <c r="G34" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="H34" t="s">
         <v>87</v>
@@ -5638,10 +6165,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="B35" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C35" t="s">
         <v>15</v>
@@ -5650,13 +6177,13 @@
         <v>111</v>
       </c>
       <c r="E35" t="s">
-        <v>344</v>
+        <v>374</v>
       </c>
       <c r="F35" t="s">
         <v>12</v>
       </c>
       <c r="G35" t="s">
-        <v>345</v>
+        <v>375</v>
       </c>
       <c r="H35" t="s">
         <v>87</v>
@@ -5664,10 +6191,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="B36" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C36" t="s">
         <v>18</v>
@@ -5676,13 +6203,13 @@
         <v>908</v>
       </c>
       <c r="E36" t="s">
-        <v>346</v>
+        <v>376</v>
       </c>
       <c r="F36" t="s">
         <v>12</v>
       </c>
       <c r="G36" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
       <c r="H36" t="s">
         <v>87</v>
@@ -5690,10 +6217,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="B37" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C37" t="s">
         <v>21</v>
@@ -5702,13 +6229,13 @@
         <v>1289</v>
       </c>
       <c r="E37" t="s">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="F37" t="s">
         <v>12</v>
       </c>
       <c r="G37" t="s">
-        <v>349</v>
+        <v>379</v>
       </c>
       <c r="H37" t="s">
         <v>87</v>
@@ -5716,10 +6243,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="B38" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C38" t="s">
         <v>10</v>
@@ -5728,13 +6255,13 @@
         <v>184</v>
       </c>
       <c r="E38" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="F38" t="s">
         <v>12</v>
       </c>
       <c r="G38" t="s">
-        <v>352</v>
+        <v>382</v>
       </c>
       <c r="H38" t="s">
         <v>87</v>
@@ -5742,10 +6269,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="B39" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C39" t="s">
         <v>15</v>
@@ -5754,13 +6281,13 @@
         <v>320</v>
       </c>
       <c r="E39" t="s">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="F39" t="s">
         <v>12</v>
       </c>
       <c r="G39" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="H39" t="s">
         <v>87</v>
@@ -5768,10 +6295,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="B40" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C40" t="s">
         <v>18</v>
@@ -5780,13 +6307,13 @@
         <v>1121</v>
       </c>
       <c r="E40" t="s">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="F40" t="s">
         <v>12</v>
       </c>
       <c r="G40" t="s">
-        <v>356</v>
+        <v>386</v>
       </c>
       <c r="H40" t="s">
         <v>87</v>
@@ -5794,10 +6321,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="B41" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C41" t="s">
         <v>21</v>
@@ -5806,13 +6333,13 @@
         <v>396</v>
       </c>
       <c r="E41" t="s">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="F41" t="s">
         <v>12</v>
       </c>
       <c r="G41" t="s">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="H41" t="s">
         <v>87</v>
@@ -5820,10 +6347,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="B42" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C42" t="s">
         <v>10</v>
@@ -5832,13 +6359,13 @@
         <v>2366</v>
       </c>
       <c r="E42" t="s">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="F42" t="s">
         <v>12</v>
       </c>
       <c r="G42" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="H42" t="s">
         <v>87</v>
@@ -5846,10 +6373,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="B43" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C43" t="s">
         <v>15</v>
@@ -5858,13 +6385,13 @@
         <v>1496</v>
       </c>
       <c r="E43" t="s">
-        <v>361</v>
+        <v>391</v>
       </c>
       <c r="F43" t="s">
         <v>12</v>
       </c>
       <c r="G43" t="s">
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="H43" t="s">
         <v>87</v>
@@ -5872,10 +6399,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="B44" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C44" t="s">
         <v>18</v>
@@ -5884,13 +6411,13 @@
         <v>77</v>
       </c>
       <c r="E44" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="F44" t="s">
         <v>12</v>
       </c>
       <c r="G44" t="s">
-        <v>364</v>
+        <v>394</v>
       </c>
       <c r="H44" t="s">
         <v>87</v>
@@ -5898,10 +6425,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="B45" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C45" t="s">
         <v>21</v>
@@ -5910,13 +6437,13 @@
         <v>1918</v>
       </c>
       <c r="E45" t="s">
-        <v>365</v>
+        <v>395</v>
       </c>
       <c r="F45" t="s">
         <v>12</v>
       </c>
       <c r="G45" t="s">
-        <v>366</v>
+        <v>396</v>
       </c>
       <c r="H45" t="s">
         <v>87</v>
@@ -5924,10 +6451,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="B46" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C46" t="s">
         <v>10</v>
@@ -5936,13 +6463,13 @@
         <v>2651</v>
       </c>
       <c r="E46" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="F46" t="s">
         <v>12</v>
       </c>
       <c r="G46" t="s">
-        <v>369</v>
+        <v>399</v>
       </c>
       <c r="H46" t="s">
         <v>87</v>
@@ -5950,10 +6477,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="B47" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C47" t="s">
         <v>15</v>
@@ -5962,13 +6489,13 @@
         <v>508</v>
       </c>
       <c r="E47" t="s">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="F47" t="s">
         <v>12</v>
       </c>
       <c r="G47" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="H47" t="s">
         <v>87</v>
@@ -5976,10 +6503,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="B48" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C48" t="s">
         <v>18</v>
@@ -5988,13 +6515,13 @@
         <v>2003</v>
       </c>
       <c r="E48" t="s">
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="F48" t="s">
         <v>12</v>
       </c>
       <c r="G48" t="s">
-        <v>373</v>
+        <v>403</v>
       </c>
       <c r="H48" t="s">
         <v>87</v>
@@ -6002,10 +6529,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="B49" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C49" t="s">
         <v>21</v>
@@ -6014,13 +6541,13 @@
         <v>1019</v>
       </c>
       <c r="E49" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
       <c r="F49" t="s">
         <v>12</v>
       </c>
       <c r="G49" t="s">
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="H49" t="s">
         <v>87</v>
@@ -6028,10 +6555,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="B50" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C50" t="s">
         <v>10</v>
@@ -6040,13 +6567,13 @@
         <v>1930</v>
       </c>
       <c r="E50" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="F50" t="s">
         <v>12</v>
       </c>
       <c r="G50" t="s">
-        <v>377</v>
+        <v>407</v>
       </c>
       <c r="H50" t="s">
         <v>87</v>
@@ -6054,10 +6581,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="B51" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C51" t="s">
         <v>15</v>
@@ -6066,13 +6593,13 @@
         <v>330</v>
       </c>
       <c r="E51" t="s">
-        <v>378</v>
+        <v>408</v>
       </c>
       <c r="F51" t="s">
         <v>12</v>
       </c>
       <c r="G51" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="H51" t="s">
         <v>87</v>
@@ -6080,10 +6607,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="B52" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C52" t="s">
         <v>18</v>
@@ -6092,13 +6619,13 @@
         <v>589</v>
       </c>
       <c r="E52" t="s">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="F52" t="s">
         <v>12</v>
       </c>
       <c r="G52" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="H52" t="s">
         <v>87</v>
@@ -6106,10 +6633,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="B53" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C53" t="s">
         <v>21</v>
@@ -6118,13 +6645,13 @@
         <v>1728</v>
       </c>
       <c r="E53" t="s">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
       </c>
       <c r="G53" t="s">
-        <v>383</v>
+        <v>413</v>
       </c>
       <c r="H53" t="s">
         <v>87</v>
@@ -6132,10 +6659,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="B54" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C54" t="s">
         <v>10</v>
@@ -6144,13 +6671,13 @@
         <v>1446</v>
       </c>
       <c r="E54" t="s">
-        <v>384</v>
+        <v>414</v>
       </c>
       <c r="F54" t="s">
         <v>12</v>
       </c>
       <c r="G54" t="s">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="H54" t="s">
         <v>87</v>
@@ -6158,10 +6685,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="B55" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C55" t="s">
         <v>15</v>
@@ -6170,13 +6697,13 @@
         <v>2072</v>
       </c>
       <c r="E55" t="s">
-        <v>386</v>
+        <v>416</v>
       </c>
       <c r="F55" t="s">
         <v>12</v>
       </c>
       <c r="G55" t="s">
-        <v>387</v>
+        <v>417</v>
       </c>
       <c r="H55" t="s">
         <v>87</v>
@@ -6184,10 +6711,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="B56" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C56" t="s">
         <v>18</v>
@@ -6196,13 +6723,13 @@
         <v>183</v>
       </c>
       <c r="E56" t="s">
-        <v>388</v>
+        <v>418</v>
       </c>
       <c r="F56" t="s">
         <v>12</v>
       </c>
       <c r="G56" t="s">
-        <v>389</v>
+        <v>419</v>
       </c>
       <c r="H56" t="s">
         <v>87</v>
@@ -6210,10 +6737,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="B57" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C57" t="s">
         <v>21</v>
@@ -6222,13 +6749,13 @@
         <v>2310</v>
       </c>
       <c r="E57" t="s">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="F57" t="s">
         <v>12</v>
       </c>
       <c r="G57" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
       <c r="H57" t="s">
         <v>87</v>
@@ -6236,10 +6763,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="B58" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C58" t="s">
         <v>10</v>
@@ -6248,13 +6775,13 @@
         <v>2328</v>
       </c>
       <c r="E58" t="s">
-        <v>393</v>
+        <v>423</v>
       </c>
       <c r="F58" t="s">
         <v>12</v>
       </c>
       <c r="G58" t="s">
-        <v>394</v>
+        <v>424</v>
       </c>
       <c r="H58" t="s">
         <v>87</v>
@@ -6262,10 +6789,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="B59" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C59" t="s">
         <v>15</v>
@@ -6274,13 +6801,13 @@
         <v>1472</v>
       </c>
       <c r="E59" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="F59" t="s">
         <v>12</v>
       </c>
       <c r="G59" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="H59" t="s">
         <v>87</v>
@@ -6288,10 +6815,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="B60" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C60" t="s">
         <v>18</v>
@@ -6300,13 +6827,13 @@
         <v>2370</v>
       </c>
       <c r="E60" t="s">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="F60" t="s">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="G60" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="H60" t="s">
         <v>87</v>
@@ -6314,10 +6841,10 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="B61" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C61" t="s">
         <v>21</v>
@@ -6326,13 +6853,13 @@
         <v>1145</v>
       </c>
       <c r="E61" t="s">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="F61" t="s">
         <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="H61" t="s">
         <v>87</v>
@@ -6340,10 +6867,10 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="B62" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C62" t="s">
         <v>10</v>
@@ -6352,13 +6879,13 @@
         <v>1408</v>
       </c>
       <c r="E62" t="s">
-        <v>402</v>
+        <v>432</v>
       </c>
       <c r="F62" t="s">
         <v>35</v>
       </c>
       <c r="G62" t="s">
-        <v>403</v>
+        <v>433</v>
       </c>
       <c r="H62" t="s">
         <v>87</v>
@@ -6366,10 +6893,10 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="B63" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C63" t="s">
         <v>15</v>
@@ -6378,13 +6905,13 @@
         <v>20</v>
       </c>
       <c r="E63" t="s">
-        <v>404</v>
+        <v>434</v>
       </c>
       <c r="F63" t="s">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="G63" t="s">
-        <v>405</v>
+        <v>435</v>
       </c>
       <c r="H63" t="s">
         <v>87</v>
@@ -6392,10 +6919,10 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="B64" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C64" t="s">
         <v>18</v>
@@ -6404,13 +6931,13 @@
         <v>32</v>
       </c>
       <c r="E64" t="s">
-        <v>406</v>
+        <v>436</v>
       </c>
       <c r="F64" t="s">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="G64" t="s">
-        <v>407</v>
+        <v>437</v>
       </c>
       <c r="H64" t="s">
         <v>87</v>
@@ -6418,10 +6945,10 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="B65" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C65" t="s">
         <v>21</v>
@@ -6430,13 +6957,13 @@
         <v>1344</v>
       </c>
       <c r="E65" t="s">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="F65" t="s">
         <v>12</v>
       </c>
       <c r="G65" t="s">
-        <v>409</v>
+        <v>439</v>
       </c>
       <c r="H65" t="s">
         <v>87</v>
@@ -6444,10 +6971,10 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="B66" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C66" t="s">
         <v>10</v>
@@ -6456,13 +6983,13 @@
         <v>2227</v>
       </c>
       <c r="E66" t="s">
-        <v>410</v>
+        <v>440</v>
       </c>
       <c r="F66" t="s">
         <v>35</v>
       </c>
       <c r="G66" t="s">
-        <v>411</v>
+        <v>441</v>
       </c>
       <c r="H66" t="s">
         <v>87</v>
@@ -6470,10 +6997,10 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="B67" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C67" t="s">
         <v>15</v>
@@ -6482,13 +7009,13 @@
         <v>169</v>
       </c>
       <c r="E67" t="s">
-        <v>412</v>
+        <v>442</v>
       </c>
       <c r="F67" t="s">
         <v>35</v>
       </c>
       <c r="G67" t="s">
-        <v>413</v>
+        <v>443</v>
       </c>
       <c r="H67" t="s">
         <v>87</v>
@@ -6496,10 +7023,10 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="B68" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C68" t="s">
         <v>18</v>
@@ -6508,13 +7035,13 @@
         <v>87</v>
       </c>
       <c r="E68" t="s">
-        <v>414</v>
+        <v>444</v>
       </c>
       <c r="F68" t="s">
         <v>12</v>
       </c>
       <c r="G68" t="s">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="H68" t="s">
         <v>87</v>
@@ -6522,10 +7049,10 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="B69" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C69" t="s">
         <v>21</v>
@@ -6534,13 +7061,13 @@
         <v>740</v>
       </c>
       <c r="E69" t="s">
-        <v>416</v>
+        <v>446</v>
       </c>
       <c r="F69" t="s">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="G69" t="s">
-        <v>417</v>
+        <v>447</v>
       </c>
       <c r="H69" t="s">
         <v>87</v>
@@ -6548,10 +7075,10 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="B70" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C70" t="s">
         <v>10</v>
@@ -6560,13 +7087,13 @@
         <v>1110</v>
       </c>
       <c r="E70" t="s">
-        <v>419</v>
+        <v>449</v>
       </c>
       <c r="F70" t="s">
         <v>12</v>
       </c>
       <c r="G70" t="s">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="H70" t="s">
         <v>87</v>
@@ -6574,10 +7101,10 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="B71" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C71" t="s">
         <v>15</v>
@@ -6586,13 +7113,13 @@
         <v>950</v>
       </c>
       <c r="E71" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="F71" t="s">
         <v>12</v>
       </c>
       <c r="G71" t="s">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="H71" t="s">
         <v>87</v>
@@ -6600,10 +7127,10 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="B72" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C72" t="s">
         <v>18</v>
@@ -6612,13 +7139,13 @@
         <v>1164</v>
       </c>
       <c r="E72" t="s">
-        <v>423</v>
+        <v>453</v>
       </c>
       <c r="F72" t="s">
         <v>12</v>
       </c>
       <c r="G72" t="s">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="H72" t="s">
         <v>87</v>
@@ -6626,10 +7153,10 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="B73" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C73" t="s">
         <v>21</v>
@@ -6638,13 +7165,13 @@
         <v>84</v>
       </c>
       <c r="E73" t="s">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="F73" t="s">
         <v>12</v>
       </c>
       <c r="G73" t="s">
-        <v>426</v>
+        <v>456</v>
       </c>
       <c r="H73" t="s">
         <v>87</v>
@@ -6652,10 +7179,10 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="B74" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C74" t="s">
         <v>10</v>
@@ -6664,13 +7191,13 @@
         <v>1319</v>
       </c>
       <c r="E74" t="s">
-        <v>427</v>
+        <v>457</v>
       </c>
       <c r="F74" t="s">
         <v>12</v>
       </c>
       <c r="G74" t="s">
-        <v>428</v>
+        <v>458</v>
       </c>
       <c r="H74" t="s">
         <v>87</v>
@@ -6678,10 +7205,10 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="B75" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C75" t="s">
         <v>15</v>
@@ -6690,13 +7217,13 @@
         <v>1248</v>
       </c>
       <c r="E75" t="s">
-        <v>429</v>
+        <v>459</v>
       </c>
       <c r="F75" t="s">
         <v>12</v>
       </c>
       <c r="G75" t="s">
-        <v>430</v>
+        <v>460</v>
       </c>
       <c r="H75" t="s">
         <v>87</v>
@@ -6704,10 +7231,10 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="B76" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C76" t="s">
         <v>18</v>
@@ -6716,13 +7243,13 @@
         <v>2010</v>
       </c>
       <c r="E76" t="s">
-        <v>431</v>
+        <v>461</v>
       </c>
       <c r="F76" t="s">
         <v>12</v>
       </c>
       <c r="G76" t="s">
-        <v>432</v>
+        <v>462</v>
       </c>
       <c r="H76" t="s">
         <v>87</v>
@@ -6730,10 +7257,10 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="B77" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C77" t="s">
         <v>21</v>
@@ -6742,13 +7269,13 @@
         <v>139</v>
       </c>
       <c r="E77" t="s">
-        <v>433</v>
+        <v>463</v>
       </c>
       <c r="F77" t="s">
         <v>12</v>
       </c>
       <c r="G77" t="s">
-        <v>434</v>
+        <v>464</v>
       </c>
       <c r="H77" t="s">
         <v>87</v>
@@ -6756,10 +7283,10 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>435</v>
+        <v>465</v>
       </c>
       <c r="B78" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C78" t="s">
         <v>10</v>
@@ -6768,13 +7295,13 @@
         <v>2769</v>
       </c>
       <c r="E78" t="s">
-        <v>436</v>
+        <v>466</v>
       </c>
       <c r="F78" t="s">
         <v>12</v>
       </c>
       <c r="G78" t="s">
-        <v>437</v>
+        <v>467</v>
       </c>
       <c r="H78" t="s">
         <v>87</v>
@@ -6782,10 +7309,10 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>435</v>
+        <v>465</v>
       </c>
       <c r="B79" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C79" t="s">
         <v>15</v>
@@ -6794,13 +7321,13 @@
         <v>2772</v>
       </c>
       <c r="E79" t="s">
-        <v>438</v>
+        <v>468</v>
       </c>
       <c r="F79" t="s">
         <v>12</v>
       </c>
       <c r="G79" t="s">
-        <v>439</v>
+        <v>469</v>
       </c>
       <c r="H79" t="s">
         <v>87</v>
@@ -6808,10 +7335,10 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>435</v>
+        <v>465</v>
       </c>
       <c r="B80" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C80" t="s">
         <v>18</v>
@@ -6820,13 +7347,13 @@
         <v>2771</v>
       </c>
       <c r="E80" t="s">
-        <v>440</v>
+        <v>470</v>
       </c>
       <c r="F80" t="s">
         <v>12</v>
       </c>
       <c r="G80" t="s">
-        <v>441</v>
+        <v>471</v>
       </c>
       <c r="H80" t="s">
         <v>87</v>
@@ -6834,10 +7361,10 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>435</v>
+        <v>465</v>
       </c>
       <c r="B81" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C81" t="s">
         <v>21</v>
@@ -6846,13 +7373,13 @@
         <v>2770</v>
       </c>
       <c r="E81" t="s">
-        <v>442</v>
+        <v>472</v>
       </c>
       <c r="F81" t="s">
         <v>12</v>
       </c>
       <c r="G81" t="s">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="H81" t="s">
         <v>87</v>
@@ -6860,10 +7387,10 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="B82" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C82" t="s">
         <v>10</v>
@@ -6872,13 +7399,13 @@
         <v>15</v>
       </c>
       <c r="E82" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F82" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="G82" t="s">
-        <v>446</v>
+        <v>476</v>
       </c>
       <c r="H82" t="s">
         <v>87</v>
@@ -6886,10 +7413,10 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="B83" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C83" t="s">
         <v>15</v>
@@ -6898,13 +7425,13 @@
         <v>33</v>
       </c>
       <c r="E83" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F83" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="G83" t="s">
-        <v>447</v>
+        <v>477</v>
       </c>
       <c r="H83" t="s">
         <v>87</v>
@@ -6912,10 +7439,10 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="B84" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C84" t="s">
         <v>18</v>
@@ -6924,13 +7451,13 @@
         <v>27</v>
       </c>
       <c r="E84" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F84" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="G84" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="H84" t="s">
         <v>87</v>
@@ -6938,10 +7465,10 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="B85" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C85" t="s">
         <v>21</v>
@@ -6950,13 +7477,13 @@
         <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F85" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="G85" t="s">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="H85" t="s">
         <v>87</v>
@@ -6964,10 +7491,10 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="B86" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C86" t="s">
         <v>10</v>
@@ -6976,13 +7503,13 @@
         <v>28</v>
       </c>
       <c r="E86" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F86" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="G86" t="s">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="H86" t="s">
         <v>87</v>
@@ -6990,10 +7517,10 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="B87" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C87" t="s">
         <v>15</v>
@@ -7002,13 +7529,13 @@
         <v>19</v>
       </c>
       <c r="E87" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F87" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="G87" t="s">
-        <v>451</v>
+        <v>481</v>
       </c>
       <c r="H87" t="s">
         <v>87</v>
@@ -7016,10 +7543,10 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="B88" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C88" t="s">
         <v>18</v>
@@ -7028,13 +7555,13 @@
         <v>9</v>
       </c>
       <c r="E88" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F88" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="G88" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="H88" t="s">
         <v>87</v>
@@ -7042,10 +7569,10 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="B89" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C89" t="s">
         <v>21</v>
@@ -7054,13 +7581,13 @@
         <v>5</v>
       </c>
       <c r="E89" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F89" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="G89" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="H89" t="s">
         <v>87</v>
@@ -7068,10 +7595,10 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="B90" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C90" t="s">
         <v>10</v>
@@ -7080,13 +7607,13 @@
         <v>2</v>
       </c>
       <c r="E90" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F90" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="G90" t="s">
-        <v>454</v>
+        <v>484</v>
       </c>
       <c r="H90" t="s">
         <v>87</v>
@@ -7094,10 +7621,10 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="B91" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C91" t="s">
         <v>15</v>
@@ -7106,13 +7633,13 @@
         <v>26</v>
       </c>
       <c r="E91" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F91" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="G91" t="s">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="H91" t="s">
         <v>87</v>
@@ -7120,10 +7647,10 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="B92" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C92" t="s">
         <v>18</v>
@@ -7132,13 +7659,13 @@
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F92" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="G92" t="s">
-        <v>456</v>
+        <v>486</v>
       </c>
       <c r="H92" t="s">
         <v>87</v>
@@ -7146,10 +7673,10 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="B93" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C93" t="s">
         <v>21</v>
@@ -7158,13 +7685,13 @@
         <v>35</v>
       </c>
       <c r="E93" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F93" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="G93" t="s">
-        <v>457</v>
+        <v>487</v>
       </c>
       <c r="H93" t="s">
         <v>87</v>
@@ -7172,10 +7699,10 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="B94" t="s">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="C94" t="s">
         <v>10</v>
@@ -7184,13 +7711,13 @@
         <v>10</v>
       </c>
       <c r="E94" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F94" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="G94" t="s">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="H94" t="s">
         <v>87</v>
@@ -7198,10 +7725,10 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="B95" t="s">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="C95" t="s">
         <v>15</v>
@@ -7210,13 +7737,13 @@
         <v>20</v>
       </c>
       <c r="E95" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F95" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="G95" t="s">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="H95" t="s">
         <v>87</v>
@@ -7224,10 +7751,10 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="B96" t="s">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="C96" t="s">
         <v>18</v>
@@ -7236,13 +7763,13 @@
         <v>23</v>
       </c>
       <c r="E96" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F96" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="G96" t="s">
-        <v>461</v>
+        <v>491</v>
       </c>
       <c r="H96" t="s">
         <v>87</v>
@@ -7250,10 +7777,10 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="B97" t="s">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="C97" t="s">
         <v>21</v>
@@ -7262,13 +7789,13 @@
         <v>44</v>
       </c>
       <c r="E97" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F97" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="G97" t="s">
-        <v>462</v>
+        <v>492</v>
       </c>
       <c r="H97" t="s">
         <v>87</v>
@@ -7276,10 +7803,10 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B98" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C98" t="s">
         <v>10</v>
@@ -7288,13 +7815,13 @@
         <v>462</v>
       </c>
       <c r="E98" t="s">
-        <v>463</v>
+        <v>493</v>
       </c>
       <c r="F98" t="s">
         <v>12</v>
       </c>
       <c r="G98" t="s">
-        <v>464</v>
+        <v>494</v>
       </c>
       <c r="H98" t="s">
         <v>221</v>
@@ -7302,10 +7829,10 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B99" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C99" t="s">
         <v>15</v>
@@ -7314,13 +7841,13 @@
         <v>1099</v>
       </c>
       <c r="E99" t="s">
-        <v>465</v>
+        <v>495</v>
       </c>
       <c r="F99" t="s">
         <v>12</v>
       </c>
       <c r="G99" t="s">
-        <v>466</v>
+        <v>496</v>
       </c>
       <c r="H99" t="s">
         <v>221</v>
@@ -7328,10 +7855,10 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B100" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C100" t="s">
         <v>18</v>
@@ -7340,13 +7867,13 @@
         <v>1790</v>
       </c>
       <c r="E100" t="s">
-        <v>467</v>
+        <v>497</v>
       </c>
       <c r="F100" t="s">
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="H100" t="s">
         <v>221</v>
@@ -7354,10 +7881,10 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B101" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C101" t="s">
         <v>21</v>
@@ -7366,13 +7893,13 @@
         <v>2284</v>
       </c>
       <c r="E101" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="F101" t="s">
         <v>12</v>
       </c>
       <c r="G101" t="s">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="H101" t="s">
         <v>221</v>
@@ -7380,10 +7907,10 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B102" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C102" t="s">
         <v>10</v>
@@ -7392,13 +7919,13 @@
         <v>2662</v>
       </c>
       <c r="E102" t="s">
-        <v>471</v>
+        <v>501</v>
       </c>
       <c r="F102" t="s">
         <v>12</v>
       </c>
       <c r="G102" t="s">
-        <v>472</v>
+        <v>502</v>
       </c>
       <c r="H102" t="s">
         <v>221</v>
@@ -7406,10 +7933,10 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B103" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C103" t="s">
         <v>15</v>
@@ -7418,13 +7945,13 @@
         <v>43</v>
       </c>
       <c r="E103" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="F103" t="s">
         <v>12</v>
       </c>
       <c r="G103" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="H103" t="s">
         <v>221</v>
@@ -7432,10 +7959,10 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B104" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C104" t="s">
         <v>18</v>
@@ -7444,13 +7971,13 @@
         <v>1432</v>
       </c>
       <c r="E104" t="s">
-        <v>473</v>
+        <v>503</v>
       </c>
       <c r="F104" t="s">
         <v>12</v>
       </c>
       <c r="G104" t="s">
-        <v>474</v>
+        <v>504</v>
       </c>
       <c r="H104" t="s">
         <v>221</v>
@@ -7458,10 +7985,10 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B105" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C105" t="s">
         <v>21</v>
@@ -7470,13 +7997,13 @@
         <v>566</v>
       </c>
       <c r="E105" t="s">
-        <v>475</v>
+        <v>505</v>
       </c>
       <c r="F105" t="s">
         <v>12</v>
       </c>
       <c r="G105" t="s">
-        <v>476</v>
+        <v>506</v>
       </c>
       <c r="H105" t="s">
         <v>221</v>
@@ -7484,10 +8011,10 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B106" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C106" t="s">
         <v>10</v>
@@ -7496,13 +8023,13 @@
         <v>278</v>
       </c>
       <c r="E106" t="s">
-        <v>477</v>
+        <v>507</v>
       </c>
       <c r="F106" t="s">
         <v>12</v>
       </c>
       <c r="G106" t="s">
-        <v>478</v>
+        <v>508</v>
       </c>
       <c r="H106" t="s">
         <v>221</v>
@@ -7510,10 +8037,10 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B107" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C107" t="s">
         <v>15</v>
@@ -7522,13 +8049,13 @@
         <v>428</v>
       </c>
       <c r="E107" t="s">
-        <v>479</v>
+        <v>509</v>
       </c>
       <c r="F107" t="s">
         <v>12</v>
       </c>
       <c r="G107" t="s">
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="H107" t="s">
         <v>221</v>
@@ -7536,10 +8063,10 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B108" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C108" t="s">
         <v>18</v>
@@ -7548,13 +8075,13 @@
         <v>2745</v>
       </c>
       <c r="E108" t="s">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="F108" t="s">
         <v>12</v>
       </c>
       <c r="G108" t="s">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="H108" t="s">
         <v>221</v>
@@ -7562,10 +8089,10 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B109" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C109" t="s">
         <v>21</v>
@@ -7574,16 +8101,224 @@
         <v>1050</v>
       </c>
       <c r="E109" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="F109" t="s">
         <v>12</v>
       </c>
       <c r="G109" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="H109" t="s">
         <v>221</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>474</v>
+      </c>
+      <c r="B110" t="s">
+        <v>302</v>
+      </c>
+      <c r="C110" t="s">
+        <v>10</v>
+      </c>
+      <c r="D110">
+        <v>16</v>
+      </c>
+      <c r="E110" t="s">
+        <v>475</v>
+      </c>
+      <c r="F110" t="s">
+        <v>475</v>
+      </c>
+      <c r="G110" t="s">
+        <v>513</v>
+      </c>
+      <c r="H110" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>474</v>
+      </c>
+      <c r="B111" t="s">
+        <v>302</v>
+      </c>
+      <c r="C111" t="s">
+        <v>15</v>
+      </c>
+      <c r="D111">
+        <v>1</v>
+      </c>
+      <c r="E111" t="s">
+        <v>475</v>
+      </c>
+      <c r="F111" t="s">
+        <v>475</v>
+      </c>
+      <c r="G111" t="s">
+        <v>514</v>
+      </c>
+      <c r="H111" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>474</v>
+      </c>
+      <c r="B112" t="s">
+        <v>302</v>
+      </c>
+      <c r="C112" t="s">
+        <v>18</v>
+      </c>
+      <c r="D112">
+        <v>19</v>
+      </c>
+      <c r="E112" t="s">
+        <v>475</v>
+      </c>
+      <c r="F112" t="s">
+        <v>475</v>
+      </c>
+      <c r="G112" t="s">
+        <v>484</v>
+      </c>
+      <c r="H112" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>474</v>
+      </c>
+      <c r="B113" t="s">
+        <v>302</v>
+      </c>
+      <c r="C113" t="s">
+        <v>21</v>
+      </c>
+      <c r="D113">
+        <v>33</v>
+      </c>
+      <c r="E113" t="s">
+        <v>475</v>
+      </c>
+      <c r="F113" t="s">
+        <v>475</v>
+      </c>
+      <c r="G113" t="s">
+        <v>515</v>
+      </c>
+      <c r="H113" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>474</v>
+      </c>
+      <c r="B114" t="s">
+        <v>311</v>
+      </c>
+      <c r="C114" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114">
+        <v>11</v>
+      </c>
+      <c r="E114" t="s">
+        <v>475</v>
+      </c>
+      <c r="F114" t="s">
+        <v>475</v>
+      </c>
+      <c r="G114" t="s">
+        <v>516</v>
+      </c>
+      <c r="H114" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>474</v>
+      </c>
+      <c r="B115" t="s">
+        <v>311</v>
+      </c>
+      <c r="C115" t="s">
+        <v>15</v>
+      </c>
+      <c r="D115">
+        <v>21</v>
+      </c>
+      <c r="E115" t="s">
+        <v>475</v>
+      </c>
+      <c r="F115" t="s">
+        <v>475</v>
+      </c>
+      <c r="G115" t="s">
+        <v>517</v>
+      </c>
+      <c r="H115" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>474</v>
+      </c>
+      <c r="B116" t="s">
+        <v>311</v>
+      </c>
+      <c r="C116" t="s">
+        <v>18</v>
+      </c>
+      <c r="D116">
+        <v>34</v>
+      </c>
+      <c r="E116" t="s">
+        <v>475</v>
+      </c>
+      <c r="F116" t="s">
+        <v>475</v>
+      </c>
+      <c r="G116" t="s">
+        <v>518</v>
+      </c>
+      <c r="H116" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>474</v>
+      </c>
+      <c r="B117" t="s">
+        <v>311</v>
+      </c>
+      <c r="C117" t="s">
+        <v>21</v>
+      </c>
+      <c r="D117">
+        <v>22</v>
+      </c>
+      <c r="E117" t="s">
+        <v>475</v>
+      </c>
+      <c r="F117" t="s">
+        <v>475</v>
+      </c>
+      <c r="G117" t="s">
+        <v>519</v>
+      </c>
+      <c r="H117" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
